--- a/Documents/Product Catalog/Home/Steel Almirah.xlsx
+++ b/Documents/Product Catalog/Home/Steel Almirah.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6FBE23-31D2-4032-B0E0-BD9D4DD87F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D43EB93-3E12-4E9A-9178-F130C07EC4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="64">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Steel Almirah</t>
+  </si>
+  <si>
+    <t>অবয়ব 2-Door Steel Almirah</t>
   </si>
 </sst>
 </file>
@@ -608,24 +611,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -638,10 +623,28 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2053,89 +2056,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="24" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="24"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="24" t="s">
+      <c r="L3" s="26"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="P3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="24" t="s">
+      <c r="Q3" s="26" t="s">
         <v>40</v>
       </c>
       <c r="S3" s="4"/>
@@ -2168,11 +2171,11 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="21" t="s">
         <v>13</v>
       </c>
@@ -2182,8 +2185,8 @@
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="33"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2193,10 +2196,10 @@
       <c r="M4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -3014,7 +3017,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="8" t="s">
@@ -3059,24 +3062,24 @@
       </c>
     </row>
     <row r="21" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -3107,24 +3110,24 @@
       <c r="AT21" s="4"/>
     </row>
     <row r="22" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -3155,24 +3158,24 @@
       <c r="AT22" s="4"/>
     </row>
     <row r="23" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A23" s="22"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -3203,24 +3206,24 @@
       <c r="AT23" s="4"/>
     </row>
     <row r="24" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -3251,24 +3254,24 @@
       <c r="AT24" s="4"/>
     </row>
     <row r="25" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -3299,24 +3302,24 @@
       <c r="AT25" s="4"/>
     </row>
     <row r="26" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -3347,24 +3350,24 @@
       <c r="AT26" s="4"/>
     </row>
     <row r="27" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -3395,24 +3398,24 @@
       <c r="AT27" s="4"/>
     </row>
     <row r="28" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A28" s="22"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -3443,24 +3446,24 @@
       <c r="AT28" s="4"/>
     </row>
     <row r="29" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A29" s="22"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -3491,24 +3494,24 @@
       <c r="AT29" s="4"/>
     </row>
     <row r="30" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A30" s="22"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -3539,24 +3542,24 @@
       <c r="AT30" s="4"/>
     </row>
     <row r="31" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A31" s="22"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
@@ -3587,24 +3590,24 @@
       <c r="AT31" s="4"/>
     </row>
     <row r="32" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="23"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -3635,24 +3638,24 @@
       <c r="AT32" s="4"/>
     </row>
     <row r="33" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A33" s="22"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
@@ -3683,24 +3686,24 @@
       <c r="AT33" s="4"/>
     </row>
     <row r="34" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -3731,24 +3734,24 @@
       <c r="AT34" s="4"/>
     </row>
     <row r="35" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
@@ -3779,24 +3782,24 @@
       <c r="AT35" s="4"/>
     </row>
     <row r="36" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
@@ -3827,24 +3830,24 @@
       <c r="AT36" s="4"/>
     </row>
     <row r="37" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -3875,24 +3878,24 @@
       <c r="AT37" s="4"/>
     </row>
     <row r="38" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="23"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
@@ -3923,24 +3926,24 @@
       <c r="AT38" s="4"/>
     </row>
     <row r="39" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="23"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -3971,24 +3974,24 @@
       <c r="AT39" s="4"/>
     </row>
     <row r="40" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A40" s="22"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
@@ -4019,24 +4022,24 @@
       <c r="AT40" s="4"/>
     </row>
     <row r="41" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="23"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="23"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="30"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
@@ -4067,24 +4070,24 @@
       <c r="AT41" s="4"/>
     </row>
     <row r="42" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
@@ -4115,24 +4118,24 @@
       <c r="AT42" s="4"/>
     </row>
     <row r="43" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="23"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
@@ -4163,24 +4166,24 @@
       <c r="AT43" s="4"/>
     </row>
     <row r="44" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="23"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="23"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
@@ -4211,24 +4214,24 @@
       <c r="AT44" s="4"/>
     </row>
     <row r="45" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
@@ -4259,24 +4262,24 @@
       <c r="AT45" s="4"/>
     </row>
     <row r="46" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A46" s="22"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
@@ -4307,24 +4310,24 @@
       <c r="AT46" s="4"/>
     </row>
     <row r="47" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A47" s="22"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="23"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
@@ -4355,24 +4358,24 @@
       <c r="AT47" s="4"/>
     </row>
     <row r="48" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A48" s="22"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="23"/>
-      <c r="Q48" s="23"/>
-      <c r="R48" s="23"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
@@ -4403,24 +4406,24 @@
       <c r="AT48" s="4"/>
     </row>
     <row r="49" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A49" s="22"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
@@ -4451,24 +4454,24 @@
       <c r="AT49" s="4"/>
     </row>
     <row r="50" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A50" s="22"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
@@ -4499,24 +4502,24 @@
       <c r="AT50" s="4"/>
     </row>
     <row r="51" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A51" s="22"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
@@ -4547,24 +4550,24 @@
       <c r="AT51" s="4"/>
     </row>
     <row r="52" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A52" s="22"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
@@ -4595,24 +4598,24 @@
       <c r="AT52" s="4"/>
     </row>
     <row r="53" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A53" s="22"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
       <c r="S53" s="4"/>
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
@@ -4643,24 +4646,24 @@
       <c r="AT53" s="4"/>
     </row>
     <row r="54" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A54" s="22"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
@@ -4691,24 +4694,24 @@
       <c r="AT54" s="4"/>
     </row>
     <row r="55" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="23"/>
-      <c r="Q55" s="23"/>
-      <c r="R55" s="23"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
@@ -4739,24 +4742,24 @@
       <c r="AT55" s="4"/>
     </row>
     <row r="56" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="23"/>
-      <c r="O56" s="23"/>
-      <c r="P56" s="23"/>
-      <c r="Q56" s="23"/>
-      <c r="R56" s="23"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30"/>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="30"/>
       <c r="S56" s="4"/>
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
@@ -4787,24 +4790,24 @@
       <c r="AT56" s="4"/>
     </row>
     <row r="57" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="23"/>
-      <c r="R57" s="23"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="30"/>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
@@ -4835,24 +4838,24 @@
       <c r="AT57" s="4"/>
     </row>
     <row r="58" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-      <c r="O58" s="23"/>
-      <c r="P58" s="23"/>
-      <c r="Q58" s="23"/>
-      <c r="R58" s="23"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
@@ -4883,24 +4886,24 @@
       <c r="AT58" s="4"/>
     </row>
     <row r="59" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A59" s="22"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="23"/>
-      <c r="O59" s="23"/>
-      <c r="P59" s="23"/>
-      <c r="Q59" s="23"/>
-      <c r="R59" s="23"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
@@ -4931,24 +4934,24 @@
       <c r="AT59" s="4"/>
     </row>
     <row r="60" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A60" s="22"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="23"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="23"/>
-      <c r="R60" s="23"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
@@ -4979,44 +4982,44 @@
       <c r="AT60" s="4"/>
     </row>
     <row r="61" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A61" s="22"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="23"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="23"/>
-      <c r="Q61" s="23"/>
-      <c r="R61" s="23"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
     </row>
     <row r="62" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A62" s="22"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="23"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="23"/>
-      <c r="N62" s="23"/>
-      <c r="O62" s="23"/>
-      <c r="P62" s="23"/>
-      <c r="Q62" s="23"/>
-      <c r="R62" s="23"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="30"/>
+      <c r="O62" s="30"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="30"/>
+      <c r="R62" s="30"/>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
@@ -5047,24 +5050,24 @@
       <c r="AT62" s="4"/>
     </row>
     <row r="63" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A63" s="22"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="23"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="23"/>
-      <c r="O63" s="23"/>
-      <c r="P63" s="23"/>
-      <c r="Q63" s="23"/>
-      <c r="R63" s="23"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="30"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="30"/>
       <c r="S63" s="4"/>
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
@@ -5095,24 +5098,24 @@
       <c r="AT63" s="4"/>
     </row>
     <row r="64" spans="1:46" ht="80.099999999999994" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
       <c r="S64" s="4"/>
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
@@ -8051,6 +8054,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A21:R64"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A3:A4"/>
@@ -8060,13 +8070,6 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A21:R64"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
